--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484644_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484644_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4419</v>
+        <v>3.9248</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2374</v>
+        <v>4.2653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2045</v>
+        <v>-0.3405</v>
       </c>
       <c r="G2" t="n">
         <v>3.3769</v>
@@ -610,13 +610,13 @@
         <v>1.4661</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7822</v>
+        <v>1.2651</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5294</v>
+        <v>0.5573</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2528</v>
+        <v>0.7077</v>
       </c>
       <c r="V2" t="n">
         <v>-1.267</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PEÑA</t>
+          <t>A. ALBA GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2753</v>
+        <v>2.1101</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2753</v>
+        <v>3.2568</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-1.1468</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2753</v>
+        <v>-2.2735</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6502</v>
+        <v>-1.8151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6251</v>
+        <v>-0.4584</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2753</v>
+        <v>1.491</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6502</v>
+        <v>0.5386</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6251</v>
+        <v>0.9524</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-3.7646</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-2.3537</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-1.4109</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3823</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.4123</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.3601</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.0522</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9771</v>
+        <v>1.8762</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8546</v>
+        <v>4.5556</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.8775</v>
+        <v>-2.6794</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4499</v>
@@ -766,13 +766,13 @@
         <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7562</v>
+        <v>-0.8571</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8627</v>
+        <v>-0.1617</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8935</v>
+        <v>-0.6953</v>
       </c>
       <c r="V4" t="n">
         <v>1.9005</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALBA GONZALEZ</t>
+          <t>D. ARIJA DE LA PEÑA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.956</v>
+        <v>1.2753</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9789</v>
+        <v>1.2753</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0229</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2735</v>
+        <v>1.2753</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8151</v>
+        <v>0.6502</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4584</v>
+        <v>0.6251</v>
       </c>
       <c r="J5" t="n">
-        <v>1.491</v>
+        <v>1.2753</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5386</v>
+        <v>0.6502</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9524</v>
+        <v>0.6251</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.7646</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.3537</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4109</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3823</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5656</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7417</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9177999999999999</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1761</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6783</v>
+        <v>0.5824</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8994</v>
+        <v>0.9273</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2211</v>
+        <v>-0.3449</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4487</v>
@@ -922,13 +922,13 @@
         <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1557</v>
+        <v>-0.2517</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0015</v>
+        <v>0.0264</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1542</v>
+        <v>-0.2781</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1584</v>
+        <v>-0.3478</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2202</v>
+        <v>-0.5087</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0618</v>
+        <v>0.1609</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1952</v>
@@ -1000,13 +1000,13 @@
         <v>0.3665</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3587</v>
+        <v>0.1693</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4208</v>
+        <v>0.1324</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0621</v>
+        <v>0.0369</v>
       </c>
       <c r="V7" t="n">
         <v>0.3115</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7516</v>
+        <v>-0.6059</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.5999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0555</v>
+        <v>-0.006</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6014</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1502</v>
+        <v>-0.0045</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0551</v>
+        <v>0.0411</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.0456</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.866</v>
+        <v>-1.1128</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5481</v>
+        <v>-0.9188</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3179</v>
+        <v>-0.194</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9448</v>
@@ -1156,13 +1156,13 @@
         <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>0.796</v>
+        <v>0.5492</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6946</v>
+        <v>0.3239</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1014</v>
+        <v>0.2253</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.701</v>
+        <v>-2.0339</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5296</v>
+        <v>0.5435</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2306</v>
+        <v>-2.5774</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1455</v>
@@ -1234,13 +1234,13 @@
         <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3449</v>
+        <v>1.0121</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5294</v>
+        <v>0.5434</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8155</v>
+        <v>0.4687</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6335</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4598</v>
+        <v>-2.4895</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6827</v>
+        <v>-1.8611</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7771</v>
+        <v>-0.6284</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7044</v>
@@ -1312,13 +1312,13 @@
         <v>0.1833</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0614</v>
+        <v>0.0317</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2187</v>
+        <v>0.0404</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1573</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8145</v>
+        <v>-2.6048</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4509</v>
+        <v>-2.4473</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3635</v>
+        <v>-0.1576</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1976</v>
+        <v>-1.7628</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4695</v>
+        <v>-1.2534</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.7281</v>
+        <v>-0.5093</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6493</v>
+        <v>0.0905</v>
       </c>
       <c r="K12" t="n">
-        <v>1.5882</v>
+        <v>-0.5543</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9388</v>
+        <v>0.6448</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.8469</v>
+        <v>-1.8532</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0576</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.7893</v>
+        <v>-1.1541</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1833</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.9321</v>
       </c>
       <c r="R12" t="n">
-        <v>3.1154</v>
+        <v>1.4661</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5664</v>
+        <v>0.302</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5649</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0015</v>
+        <v>0.2296</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6335</v>
+        <v>0.3219</v>
       </c>
       <c r="W12" t="n">
-        <v>1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.0941</v>
+        <v>-2.6761</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8869</v>
+        <v>-0.5603</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2071</v>
+        <v>-2.1158</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7628</v>
+        <v>-4.1976</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2534</v>
+        <v>-0.4695</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5093</v>
+        <v>-3.7281</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0905</v>
+        <v>0.6493</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.5543</v>
+        <v>1.5882</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6448</v>
+        <v>-0.9388</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8532</v>
+        <v>-4.8469</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-2.0576</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.1541</v>
+        <v>-2.7893</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="Q13" t="n">
         <v>-2.9321</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4661</v>
+        <v>3.1154</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1872</v>
+        <v>0.7048</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3673</v>
+        <v>0.4555</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1801</v>
+        <v>0.2492</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3219</v>
+        <v>0.6335</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3219</v>
+        <v>1.267</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.4201</v>
+        <v>-8.183199999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.0362</v>
+        <v>-5.0223</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.3839</v>
+        <v>-3.1609</v>
       </c>
       <c r="G14" t="n">
         <v>-5.6563</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0008</v>
+        <v>0.2377</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4193</v>
+        <v>0.4333</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4185</v>
+        <v>-0.1955</v>
       </c>
       <c r="V14" t="n">
         <v>1.267</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-11.9369</v>
+        <v>-10.2852</v>
       </c>
       <c r="E15" t="n">
-        <v>1.254099999999999</v>
+        <v>2.905399999999999</v>
       </c>
       <c r="F15" t="n">
         <v>-13.1908</v>
@@ -1615,7 +1615,7 @@
         <v>-11.543</v>
       </c>
       <c r="P15" t="n">
-        <v>2.748799999999999</v>
+        <v>2.7488</v>
       </c>
       <c r="Q15" t="n">
         <v>-13.7443</v>
@@ -1624,19 +1624,19 @@
         <v>16.4934</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9194</v>
+        <v>3.5709</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1727</v>
+        <v>2.8245</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7466</v>
+        <v>0.7464</v>
       </c>
       <c r="V15" t="n">
         <v>4.1228</v>
       </c>
       <c r="W15" t="n">
-        <v>7.9445</v>
+        <v>7.944500000000001</v>
       </c>
       <c r="X15" t="n">
         <v>-3.8217</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0218</v>
+        <v>3.8892</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0569</v>
+        <v>3.6722</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0351</v>
+        <v>0.217</v>
       </c>
       <c r="G16" t="n">
         <v>4.2326</v>
@@ -1702,13 +1702,13 @@
         <v>0.733</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8888</v>
+        <v>0.7562</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7315</v>
+        <v>0.3469</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1572</v>
+        <v>0.4093</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. YURCHENKO</t>
+          <t>M. TORTAROLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.2531</v>
+        <v>3.5183</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4697</v>
+        <v>3.2095</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2165</v>
+        <v>0.3088</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3903</v>
+        <v>1.7658</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1343</v>
+        <v>0.0959</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.744</v>
+        <v>1.6699</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1861</v>
+        <v>2.7308</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5513</v>
+        <v>1.1888</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.3652</v>
+        <v>1.5419</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7958</v>
+        <v>-0.965</v>
       </c>
       <c r="N17" t="n">
-        <v>0.583</v>
+        <v>-1.0929</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3787</v>
+        <v>0.1279</v>
       </c>
       <c r="P17" t="n">
-        <v>0.733</v>
+        <v>0.5498</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1298</v>
+        <v>0.2474</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5664</v>
+        <v>0.1177</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4366</v>
+        <v>0.1297</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6335</v>
+        <v>1.2774</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6335</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. TORTAROLO</t>
+          <t>S. YURCHENKO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.1278</v>
+        <v>3.0274</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0172</v>
+        <v>2.8927</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1106</v>
+        <v>0.1346</v>
       </c>
       <c r="G18" t="n">
-        <v>1.7658</v>
+        <v>2.3903</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0959</v>
+        <v>4.1343</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6699</v>
+        <v>-1.744</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7308</v>
+        <v>3.1861</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1888</v>
+        <v>3.5513</v>
       </c>
       <c r="L18" t="n">
-        <v>1.5419</v>
+        <v>-0.3652</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.965</v>
+        <v>-0.7958</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0929</v>
+        <v>0.583</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1279</v>
+        <v>-1.3787</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1431</v>
+        <v>-0.096</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0746</v>
+        <v>-0.0105</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0854</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2774</v>
+        <v>0.6335</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3219</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6359</v>
+        <v>2.7</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6059</v>
+        <v>1.4136</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0299</v>
+        <v>1.2863</v>
       </c>
       <c r="G19" t="n">
         <v>1.3258</v>
@@ -1936,13 +1936,13 @@
         <v>1.2828</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3492</v>
+        <v>0.4133</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6214</v>
+        <v>0.4291</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2723</v>
+        <v>-0.0159</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3219</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2987</v>
+        <v>2.2331</v>
       </c>
       <c r="E20" t="n">
         <v>0.6803</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6184</v>
+        <v>1.5528</v>
       </c>
       <c r="G20" t="n">
         <v>4.0693</v>
@@ -2014,13 +2014,13 @@
         <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3735</v>
+        <v>0.3079</v>
       </c>
       <c r="T20" t="n">
         <v>0.126</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2475</v>
+        <v>0.1819</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3115</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. BOU MIÑARRO</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6251</v>
+        <v>1.3258</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6251</v>
+        <v>0.9167999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.409</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6251</v>
+        <v>2.628</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-0.7028</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6251</v>
+        <v>3.3308</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6251</v>
+        <v>4.0114</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.6161</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6251</v>
+        <v>3.3953</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-1.3834</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-1.3189</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.0646</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-0.2472</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.3458</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>I. BOU MIÑARRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5279</v>
+        <v>0.6251</v>
       </c>
       <c r="E22" t="n">
-        <v>2.0677</v>
+        <v>0.6251</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5398</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>2.6275</v>
+        <v>0.6251</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8743</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7532</v>
+        <v>0.6251</v>
       </c>
       <c r="J22" t="n">
-        <v>2.8384</v>
+        <v>0.6251</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0466</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.6251</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2109</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1723</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9614</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9163</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1888</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1456</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3343</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.9109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5057</v>
+        <v>0.3458</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0514</v>
+        <v>1.6831</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4543</v>
+        <v>-1.3372</v>
       </c>
       <c r="G23" t="n">
-        <v>2.628</v>
+        <v>2.6275</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7028</v>
+        <v>0.8743</v>
       </c>
       <c r="I23" t="n">
-        <v>3.3308</v>
+        <v>1.7532</v>
       </c>
       <c r="J23" t="n">
-        <v>4.0114</v>
+        <v>2.8384</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6161</v>
+        <v>2.0466</v>
       </c>
       <c r="L23" t="n">
-        <v>3.3953</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3834</v>
+        <v>-0.2109</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3189</v>
+        <v>-1.1723</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0646</v>
+        <v>0.9614</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.733</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0674</v>
+        <v>-0.3709</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2111</v>
+        <v>-0.2391</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1438</v>
+        <v>-0.1318</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3219</v>
+        <v>-1.9109</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3219</v>
+        <v>-1.9109</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8576</v>
       </c>
       <c r="E24" t="n">
         <v>-1.6842</v>
       </c>
       <c r="F24" t="n">
-        <v>0.847</v>
+        <v>0.8266</v>
       </c>
       <c r="G24" t="n">
         <v>0.5802</v>
@@ -2326,13 +2326,13 @@
         <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1346</v>
+        <v>-0.155</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1346</v>
+        <v>-0.155</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.8045</v>
+        <v>-1.3601</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7747000000000001</v>
+        <v>-0.5824</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0298</v>
+        <v>-0.7776999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>1.1937</v>
@@ -2404,13 +2404,13 @@
         <v>2.1991</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7862</v>
+        <v>-1.3418</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.046</v>
+        <v>-0.8537</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7402</v>
+        <v>-0.4881</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5785</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.4176</v>
+        <v>-2.2282</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0755</v>
+        <v>0.364</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.4931</v>
+        <v>-2.5922</v>
       </c>
       <c r="G26" t="n">
         <v>-0.7105</v>
@@ -2482,13 +2482,13 @@
         <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.3406</v>
+        <v>-0.1512</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6056</v>
+        <v>-0.3171</v>
       </c>
       <c r="U26" t="n">
-        <v>0.265</v>
+        <v>0.1659</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6335</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>11.9367</v>
+        <v>13.2188</v>
       </c>
       <c r="E27" t="n">
-        <v>13.1908</v>
+        <v>13.1907</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.2541</v>
+        <v>0.02800000000000002</v>
       </c>
       <c r="G27" t="n">
         <v>20.7278</v>
@@ -2560,13 +2560,13 @@
         <v>13.7443</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.9194</v>
+        <v>-0.6373000000000002</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.7464000000000002</v>
+        <v>-0.7464999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.173</v>
+        <v>0.1092</v>
       </c>
       <c r="V27" t="n">
         <v>-4.1228</v>
